--- a/output/pdf_financials_xlsx/MNRG.xlsx
+++ b/output/pdf_financials_xlsx/MNRG.xlsx
@@ -2830,19 +2830,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.344231</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.600594</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.803594</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.977888</v>
       </c>
     </row>
     <row r="93">
@@ -3459,16 +3459,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0424</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.005</v>
+        <v>-0.216748</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.49023</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.873001</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>3.030689</v>
@@ -4538,7 +4538,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -4988,7 +4992,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -5260,7 +5268,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -6200,7 +6212,11 @@
           <t>Reserves 5 1,344,231</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -8130,7 +8146,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>-0.0424</v>
       </c>

--- a/output/pdf_financials_xlsx/MNRG.xlsx
+++ b/output/pdf_financials_xlsx/MNRG.xlsx
@@ -738,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.024277</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.071453</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.014385</v>
       </c>
     </row>
     <row r="13">
@@ -1157,13 +1157,13 @@
         <v>-2.440067</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.116572</v>
+        <v>-1.140849</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.720346</v>
+        <v>-3.791799</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.710817</v>
+        <v>-4.725202</v>
       </c>
     </row>
     <row r="28">
@@ -1207,13 +1207,13 @@
         <v>-2.440067</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.116572</v>
+        <v>-1.140849</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.720346</v>
+        <v>-3.791799</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.710817</v>
+        <v>-4.725202</v>
       </c>
     </row>
     <row r="30">
@@ -1329,22 +1329,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.365852</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.554498</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.064081</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.146638</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.25525</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.033469</v>
       </c>
     </row>
     <row r="35">
@@ -1379,22 +1379,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.365852</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.554498</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.064081</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.146638</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.1634</v>
+        <v>2.41865</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.384107</v>
+        <v>0.417576</v>
       </c>
     </row>
     <row r="37">
@@ -1679,22 +1679,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.365852</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.554498</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.124081</v>
+        <v>0.06</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.153194</v>
+        <v>0.006556</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.311915</v>
+        <v>0.056665</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.048469</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="49">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">

--- a/output/pdf_financials_xlsx/MNRG.xlsx
+++ b/output/pdf_financials_xlsx/MNRG.xlsx
@@ -8500,7 +8500,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -10596,7 +10600,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
